--- a/artifacts/agentic-mvp/agentic-budget.xlsx
+++ b/artifacts/agentic-mvp/agentic-budget.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Category usage'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Category costs'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Monthly category summary'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Profiles'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Profiles'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Scenarios'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Additional costs'!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Pricing'!$A$1:$R$3</definedName>
@@ -1738,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1748,7 +1748,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1787,11 +1786,6 @@
           <t>cache_write_fraction</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>model_id</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1829,7 +1823,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1867,7 +1860,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1905,10 +1897,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2555,7 +2546,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Schema 7; defaults 1</t>
+          <t>Schema 8; defaults 1</t>
         </is>
       </c>
     </row>
